--- a/DateBase/orders/Nha Thu_2026-5-31.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-31.xlsx
@@ -520,6 +520,9 @@
       <c r="C11" t="str">
         <v>770_弯葱_undefined_undefined_10stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -578,7 +581,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>032051010555100</v>
+        <v>032051010555105</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-5-31.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-31.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -524,9 +524,94 @@
         <v>5</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3</v>
+      </c>
+      <c r="C12" t="str">
+        <v>47_拉丝玫红_Spider Dark Pink_Gerbera L._20stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>594_绿毛球_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>615_康乃馨野马_horse_undefined_20stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="A15" t="str">
+        <v>4</v>
+      </c>
+      <c r="C15" t="str" xml:space="preserve">
+        <v xml:space="preserve">448_吊米 绿_hanging amaranthus
+green_undefined_1bunch</v>
+      </c>
+      <c r="F15" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="C16" t="str" xml:space="preserve">
+        <v xml:space="preserve">542_吊米 红_hanging amaranthus
+red_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>244_繁星_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>113_绣球安娜绿_Hydrangea Anna Green_Hydrangea L._1stem</v>
+      </c>
+      <c r="F19" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>615_康乃馨野马_horse_undefined_20stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -581,7 +666,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>032051010555105</v>
+        <v>032051010555105102071010572080</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-5-31.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-31.xlsx
@@ -608,6 +608,9 @@
       <c r="C21" t="str">
         <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
       </c>
+      <c r="F21" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -666,7 +669,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>032051010555105102071010572080</v>
+        <v>0320510105551051020710105720810</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-5-31.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-31.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -612,9 +612,25 @@
         <v>10</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>5</v>
+      </c>
+      <c r="C22" t="str">
+        <v>329_柔丝_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L23"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -669,7 +685,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0320510105551051020710105720810</v>
+        <v>0320510105551051020710105720810100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-5-31.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-31.xlsx
@@ -627,6 +627,9 @@
       <c r="C23" t="str">
         <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
+      <c r="F23" t="str">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -685,7 +688,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0320510105551051020710105720810100</v>
+        <v>03205101055510510207101057208101015</v>
       </c>
     </row>
   </sheetData>
